--- a/survey_templates/042_management_consulting_value_survey--survey_templates.xlsx
+++ b/survey_templates/042_management_consulting_value_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your perception of the project value?</t>
+          <t>Project Value</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your level of satisfaction with the project?</t>
+          <t>Satisfaction with the Project</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>outcomes</t>
+          <t>project_outcome</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What do you think is the main outcome of our consulting relationship?</t>
+          <t>Main Outcome of Our Consulting Relationship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_outcome</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What do you think is the main outcome of our consulting relationship?</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date of Completion</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Preferred Time of Day</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>management_consulting_value</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Value of Our Management Consulting Relationship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>management_consulting_value</t>
+          <t>project_outcome_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Management Consulting Value</t>
+          <t>Outcome 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project_outcome_1</t>
+          <t>project_outcome_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Project Outcome 1</t>
+          <t>Outcome 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,200 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project_outcome_2</t>
+          <t>project_outcome_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Project Outcome 2</t>
+          <t>Outcome 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>project_outcome_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Project Outcome 3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>project_outcome_4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Project Outcome 4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>project_outcome_5</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Project Outcome 5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>project_outcome_6</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Project Outcome 6</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>project_outcome_7</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Project Outcome 7</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>project_outcome_8</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Project Outcome 8</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>project_value</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is your perception of the project value?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>satisfaction</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is your level of satisfaction with the project?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -983,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -1033,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>moderately_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Moderately Satisfied</t>
         </is>
       </c>
     </row>
@@ -1050,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1067,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1084,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1101,29 +917,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>management_consulting_value_choices</t>
+          <t>project_outcome_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1135,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>very_valuable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Very Valuable</t>
         </is>
       </c>
     </row>
@@ -1152,63 +968,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>somewhat_valuable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Somewhat Valuable</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>management_consulting_value_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>not_valuable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Not Valuable</t>
         </is>
       </c>
     </row>
